--- a/Circuit Examples/Symmetrical OTA/Symmetrical_OTA_v1.xlsx
+++ b/Circuit Examples/Symmetrical OTA/Symmetrical_OTA_v1.xlsx
@@ -1557,13 +1557,13 @@
         <v>1.5e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.243613625531462e-06</v>
+        <v>7.243613625531464e-06</v>
       </c>
       <c r="F8" t="n">
         <v>2.8e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02070789632833219</v>
+        <v>0.02070789632833218</v>
       </c>
       <c r="H8" t="n">
         <v>5.099999999999999e-14</v>
@@ -1584,19 +1584,19 @@
         <v>19.08995072849367</v>
       </c>
       <c r="N8" t="n">
-        <v>0.236814892138771</v>
+        <v>0.2368148921387711</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1941105673268615</v>
+        <v>0.1941105673268616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.248572218383732</v>
+        <v>0.2485722183837321</v>
       </c>
       <c r="R8" t="n">
-        <v>5.670771322395938e-07</v>
+        <v>5.670771322395936e-07</v>
       </c>
       <c r="S8" t="n">
         <v>2.210308494316021e-06</v>
@@ -1605,25 +1605,25 @@
         <v>1.811728274029525e-06</v>
       </c>
       <c r="U8" t="n">
-        <v>2.811253804573583e-08</v>
+        <v>2.811253804573582e-08</v>
       </c>
       <c r="V8" t="n">
         <v>0.7718174262684649</v>
       </c>
       <c r="W8" t="n">
-        <v>1.674654021543764e-14</v>
+        <v>1.674654021543765e-14</v>
       </c>
       <c r="X8" t="n">
-        <v>9.791899266239188e-15</v>
+        <v>9.791899266239191e-15</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.254115581003e-15</v>
+        <v>1.254115581003001e-15</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.154217838572621e-15</v>
+        <v>2.154217838572622e-15</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1650,13 +1650,13 @@
         <v>7.527879999999998e-17</v>
       </c>
       <c r="AJ8" t="n">
-        <v>9.889924266239188e-15</v>
+        <v>9.889924266239191e-15</v>
       </c>
       <c r="AK8" t="n">
         <v>9.8025e-17</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.254115581003067e-15</v>
+        <v>1.254115581003068e-15</v>
       </c>
       <c r="AM8" t="n">
         <v>2.229496638572622e-15</v>
@@ -1685,13 +1685,13 @@
         <v>1.5e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>7.243613625531462e-06</v>
+        <v>7.243613625531464e-06</v>
       </c>
       <c r="F9" t="n">
         <v>2.8e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02070789632833219</v>
+        <v>0.02070789632833218</v>
       </c>
       <c r="H9" t="n">
         <v>5.099999999999999e-14</v>
@@ -1712,19 +1712,19 @@
         <v>19.08995072849367</v>
       </c>
       <c r="N9" t="n">
-        <v>0.236814892138771</v>
+        <v>0.2368148921387711</v>
       </c>
       <c r="O9" t="n">
         <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1941105673268615</v>
+        <v>0.1941105673268616</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.248572218383732</v>
+        <v>0.2485722183837321</v>
       </c>
       <c r="R9" t="n">
-        <v>5.670771322395938e-07</v>
+        <v>5.670771322395936e-07</v>
       </c>
       <c r="S9" t="n">
         <v>2.210308494316021e-06</v>
@@ -1733,25 +1733,25 @@
         <v>1.811728274029525e-06</v>
       </c>
       <c r="U9" t="n">
-        <v>2.811253804573583e-08</v>
+        <v>2.811253804573582e-08</v>
       </c>
       <c r="V9" t="n">
         <v>0.7718174262684649</v>
       </c>
       <c r="W9" t="n">
-        <v>1.674654021543764e-14</v>
+        <v>1.674654021543765e-14</v>
       </c>
       <c r="X9" t="n">
-        <v>9.791899266239188e-15</v>
+        <v>9.791899266239191e-15</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.254115581003e-15</v>
+        <v>1.254115581003001e-15</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.154217838572621e-15</v>
+        <v>2.154217838572622e-15</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1778,13 +1778,13 @@
         <v>7.527879999999998e-17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>9.889924266239188e-15</v>
+        <v>9.889924266239191e-15</v>
       </c>
       <c r="AK9" t="n">
         <v>9.8025e-17</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.254115581003067e-15</v>
+        <v>1.254115581003068e-15</v>
       </c>
       <c r="AM9" t="n">
         <v>2.229496638572622e-15</v>
